--- a/evac_by_zip/evac_by_zip_2026-07-29.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-07-29.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="By ZIP Code" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Zone Detail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By ZIP Code" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zone Detail" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -693,7 +693,11 @@
           <t>Harney</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -723,7 +727,11 @@
           <t>Harney</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -821,7 +829,11 @@
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -887,7 +899,11 @@
           <t>Baker</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -985,7 +1001,11 @@
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1087,7 +1107,11 @@
           <t>Baker</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1191,7 +1215,11 @@
           <t>Baker</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1263,7 +1291,11 @@
           <t>Baker</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -1295,7 +1327,11 @@
           <t>Wasco, Wheeler</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr"/>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -1329,7 +1365,11 @@
           <t>Union</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr"/>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -1397,7 +1437,11 @@
           <t>Wheeler</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr"/>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -1505,7 +1549,11 @@
           <t>Crook</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr"/>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -1539,7 +1587,11 @@
           <t>Baker</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr"/>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
@@ -1569,7 +1621,11 @@
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr"/>
-      <c r="H32" s="12" t="inlineStr"/>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -1603,7 +1659,11 @@
           <t>Wheeler</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr"/>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -1637,7 +1697,11 @@
           <t>Harney</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr"/>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -1709,7 +1773,11 @@
           <t>Harney</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr"/>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
@@ -1781,7 +1849,11 @@
           <t>Wasco</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr"/>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -3200,7 +3272,7 @@
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D40" s="18" t="inlineStr">
@@ -3235,7 +3307,7 @@
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D41" s="18" t="inlineStr">
@@ -3270,7 +3342,7 @@
       </c>
       <c r="C42" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
@@ -3305,7 +3377,7 @@
       </c>
       <c r="C43" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
@@ -3340,7 +3412,7 @@
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
@@ -3375,7 +3447,7 @@
       </c>
       <c r="C45" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
@@ -3410,7 +3482,7 @@
       </c>
       <c r="C46" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
@@ -3445,7 +3517,7 @@
       </c>
       <c r="C47" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
@@ -3480,7 +3552,7 @@
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
@@ -3515,7 +3587,7 @@
       </c>
       <c r="C49" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
@@ -3550,7 +3622,7 @@
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
@@ -3585,7 +3657,7 @@
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
@@ -3620,7 +3692,7 @@
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
@@ -3655,7 +3727,7 @@
       </c>
       <c r="C53" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
@@ -3690,7 +3762,7 @@
       </c>
       <c r="C54" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
@@ -3725,7 +3797,7 @@
       </c>
       <c r="C55" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
@@ -3760,7 +3832,7 @@
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
@@ -3795,7 +3867,7 @@
       </c>
       <c r="C57" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
@@ -3830,7 +3902,7 @@
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
@@ -3865,7 +3937,7 @@
       </c>
       <c r="C59" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
@@ -3900,7 +3972,7 @@
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
@@ -3935,7 +4007,7 @@
       </c>
       <c r="C61" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
@@ -3970,7 +4042,7 @@
       </c>
       <c r="C62" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
@@ -4005,7 +4077,7 @@
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
@@ -4040,7 +4112,7 @@
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
@@ -4075,7 +4147,7 @@
       </c>
       <c r="C65" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
@@ -4110,7 +4182,7 @@
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
@@ -4145,7 +4217,7 @@
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D67" s="18" t="inlineStr">
@@ -4180,7 +4252,7 @@
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D68" s="18" t="inlineStr">
@@ -4215,7 +4287,7 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D69" s="18" t="inlineStr">
@@ -4250,7 +4322,7 @@
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D70" s="18" t="inlineStr">
@@ -4285,7 +4357,7 @@
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D71" s="18" t="inlineStr">
@@ -4320,7 +4392,7 @@
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D72" s="18" t="inlineStr">
@@ -4355,7 +4427,7 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D73" s="18" t="inlineStr">
@@ -4390,7 +4462,7 @@
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -4425,7 +4497,7 @@
       </c>
       <c r="C75" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -4460,7 +4532,7 @@
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -4495,7 +4567,7 @@
       </c>
       <c r="C77" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -4530,7 +4602,7 @@
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -4565,7 +4637,7 @@
       </c>
       <c r="C79" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -4600,7 +4672,7 @@
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -4635,7 +4707,7 @@
       </c>
       <c r="C81" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
@@ -4670,7 +4742,7 @@
       </c>
       <c r="C82" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
@@ -4705,7 +4777,7 @@
       </c>
       <c r="C83" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
@@ -4740,7 +4812,7 @@
       </c>
       <c r="C84" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
@@ -4775,7 +4847,7 @@
       </c>
       <c r="C85" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D85" s="18" t="inlineStr">
@@ -4810,7 +4882,7 @@
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D86" s="18" t="inlineStr">
@@ -4845,7 +4917,7 @@
       </c>
       <c r="C87" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D87" s="18" t="inlineStr">
@@ -4880,7 +4952,7 @@
       </c>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D88" s="18" t="inlineStr">
@@ -4915,7 +4987,7 @@
       </c>
       <c r="C89" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D89" s="18" t="inlineStr">
@@ -4950,7 +5022,7 @@
       </c>
       <c r="C90" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D90" s="18" t="inlineStr">
@@ -4985,7 +5057,7 @@
       </c>
       <c r="C91" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D91" s="18" t="inlineStr">
@@ -5020,7 +5092,7 @@
       </c>
       <c r="C92" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D92" s="18" t="inlineStr">
@@ -5055,7 +5127,7 @@
       </c>
       <c r="C93" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D93" s="18" t="inlineStr">
@@ -5090,7 +5162,7 @@
       </c>
       <c r="C94" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D94" s="18" t="inlineStr">
@@ -5125,7 +5197,7 @@
       </c>
       <c r="C95" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D95" s="18" t="inlineStr">
@@ -5160,7 +5232,7 @@
       </c>
       <c r="C96" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D96" s="18" t="inlineStr">
@@ -5195,7 +5267,7 @@
       </c>
       <c r="C97" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D97" s="18" t="inlineStr">
@@ -5230,7 +5302,7 @@
       </c>
       <c r="C98" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D98" s="18" t="inlineStr">
@@ -5265,7 +5337,7 @@
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D99" s="18" t="inlineStr">
@@ -5300,7 +5372,7 @@
       </c>
       <c r="C100" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D100" s="18" t="inlineStr">
@@ -5335,7 +5407,7 @@
       </c>
       <c r="C101" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D101" s="20" t="inlineStr">
@@ -5370,7 +5442,7 @@
       </c>
       <c r="C102" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
@@ -5405,7 +5477,7 @@
       </c>
       <c r="C103" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
@@ -5440,7 +5512,7 @@
       </c>
       <c r="C104" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
@@ -5475,7 +5547,7 @@
       </c>
       <c r="C105" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
@@ -5510,7 +5582,7 @@
       </c>
       <c r="C106" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
@@ -5545,7 +5617,7 @@
       </c>
       <c r="C107" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
@@ -5580,7 +5652,7 @@
       </c>
       <c r="C108" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
@@ -6385,7 +6457,7 @@
       </c>
       <c r="C131" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D131" s="16" t="inlineStr">
@@ -6420,7 +6492,7 @@
       </c>
       <c r="C132" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D132" s="16" t="inlineStr">
@@ -6490,7 +6562,7 @@
       </c>
       <c r="C134" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D134" s="18" t="inlineStr">
@@ -6595,7 +6667,7 @@
       </c>
       <c r="C137" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D137" s="18" t="inlineStr">
@@ -6665,7 +6737,7 @@
       </c>
       <c r="C139" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D139" s="18" t="inlineStr">
@@ -6735,7 +6807,7 @@
       </c>
       <c r="C141" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D141" s="18" t="inlineStr">
@@ -6805,7 +6877,7 @@
       </c>
       <c r="C143" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D143" s="18" t="inlineStr">
@@ -6875,7 +6947,7 @@
       </c>
       <c r="C145" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D145" s="18" t="inlineStr">
@@ -6910,7 +6982,7 @@
       </c>
       <c r="C146" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D146" s="18" t="inlineStr">
@@ -7015,7 +7087,7 @@
       </c>
       <c r="C149" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D149" s="20" t="inlineStr">
@@ -7085,7 +7157,7 @@
       </c>
       <c r="C151" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D151" s="20" t="inlineStr">
@@ -7155,7 +7227,7 @@
       </c>
       <c r="C153" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D153" s="16" t="inlineStr">
@@ -7190,7 +7262,7 @@
       </c>
       <c r="C154" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D154" s="16" t="inlineStr">
@@ -7225,7 +7297,7 @@
       </c>
       <c r="C155" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D155" s="16" t="inlineStr">
@@ -7260,7 +7332,7 @@
       </c>
       <c r="C156" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D156" s="16" t="inlineStr">
@@ -7295,7 +7367,7 @@
       </c>
       <c r="C157" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D157" s="18" t="inlineStr">
@@ -7330,7 +7402,7 @@
       </c>
       <c r="C158" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D158" s="18" t="inlineStr">
@@ -7365,7 +7437,7 @@
       </c>
       <c r="C159" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D159" s="18" t="inlineStr">
@@ -7400,7 +7472,7 @@
       </c>
       <c r="C160" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D160" s="18" t="inlineStr">
@@ -7435,7 +7507,7 @@
       </c>
       <c r="C161" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D161" s="18" t="inlineStr">
@@ -7470,7 +7542,7 @@
       </c>
       <c r="C162" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D162" s="18" t="inlineStr">
@@ -7505,7 +7577,7 @@
       </c>
       <c r="C163" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D163" s="18" t="inlineStr">
@@ -7540,7 +7612,7 @@
       </c>
       <c r="C164" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D164" s="18" t="inlineStr">
@@ -7575,7 +7647,7 @@
       </c>
       <c r="C165" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D165" s="18" t="inlineStr">
@@ -7610,7 +7682,7 @@
       </c>
       <c r="C166" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D166" s="18" t="inlineStr">
@@ -7645,7 +7717,7 @@
       </c>
       <c r="C167" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D167" s="18" t="inlineStr">
@@ -7680,7 +7752,7 @@
       </c>
       <c r="C168" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D168" s="18" t="inlineStr">
@@ -7715,7 +7787,7 @@
       </c>
       <c r="C169" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D169" s="18" t="inlineStr">
@@ -7750,7 +7822,7 @@
       </c>
       <c r="C170" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D170" s="18" t="inlineStr">
@@ -7785,7 +7857,7 @@
       </c>
       <c r="C171" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D171" s="18" t="inlineStr">
@@ -7820,7 +7892,7 @@
       </c>
       <c r="C172" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D172" s="18" t="inlineStr">
@@ -7855,7 +7927,7 @@
       </c>
       <c r="C173" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D173" s="18" t="inlineStr">
@@ -7890,7 +7962,7 @@
       </c>
       <c r="C174" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D174" s="18" t="inlineStr">
@@ -7925,7 +7997,7 @@
       </c>
       <c r="C175" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D175" s="18" t="inlineStr">
@@ -7960,7 +8032,7 @@
       </c>
       <c r="C176" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D176" s="18" t="inlineStr">
@@ -7995,7 +8067,7 @@
       </c>
       <c r="C177" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D177" s="18" t="inlineStr">
@@ -8030,7 +8102,7 @@
       </c>
       <c r="C178" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D178" s="18" t="inlineStr">
@@ -8065,7 +8137,7 @@
       </c>
       <c r="C179" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D179" s="20" t="inlineStr">
@@ -8100,7 +8172,7 @@
       </c>
       <c r="C180" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D180" s="20" t="inlineStr">
@@ -9305,7 +9377,7 @@
       </c>
       <c r="C215" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D215" s="16" t="inlineStr">
@@ -9340,7 +9412,7 @@
       </c>
       <c r="C216" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D216" s="16" t="inlineStr">
@@ -9375,7 +9447,7 @@
       </c>
       <c r="C217" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D217" s="16" t="inlineStr">
@@ -9410,7 +9482,7 @@
       </c>
       <c r="C218" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D218" s="16" t="inlineStr">
@@ -9445,7 +9517,7 @@
       </c>
       <c r="C219" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D219" s="16" t="inlineStr">
@@ -9480,7 +9552,7 @@
       </c>
       <c r="C220" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D220" s="16" t="inlineStr">
@@ -9515,7 +9587,7 @@
       </c>
       <c r="C221" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D221" s="16" t="inlineStr">
@@ -9550,7 +9622,7 @@
       </c>
       <c r="C222" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D222" s="16" t="inlineStr">
@@ -9585,7 +9657,7 @@
       </c>
       <c r="C223" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D223" s="16" t="inlineStr">
@@ -9620,7 +9692,7 @@
       </c>
       <c r="C224" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D224" s="18" t="inlineStr">
@@ -9655,7 +9727,7 @@
       </c>
       <c r="C225" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D225" s="18" t="inlineStr">
@@ -9690,7 +9762,7 @@
       </c>
       <c r="C226" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D226" s="18" t="inlineStr">
@@ -9725,7 +9797,7 @@
       </c>
       <c r="C227" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D227" s="18" t="inlineStr">
@@ -9760,7 +9832,7 @@
       </c>
       <c r="C228" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D228" s="18" t="inlineStr">
@@ -9795,7 +9867,7 @@
       </c>
       <c r="C229" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D229" s="18" t="inlineStr">
@@ -9830,7 +9902,7 @@
       </c>
       <c r="C230" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D230" s="18" t="inlineStr">
@@ -9865,7 +9937,7 @@
       </c>
       <c r="C231" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D231" s="16" t="inlineStr">
@@ -9900,7 +9972,7 @@
       </c>
       <c r="C232" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D232" s="16" t="inlineStr">
@@ -9935,7 +10007,7 @@
       </c>
       <c r="C233" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D233" s="16" t="inlineStr">
@@ -9970,7 +10042,7 @@
       </c>
       <c r="C234" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D234" s="16" t="inlineStr">
@@ -10005,7 +10077,7 @@
       </c>
       <c r="C235" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D235" s="16" t="inlineStr">
@@ -10040,7 +10112,7 @@
       </c>
       <c r="C236" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D236" s="16" t="inlineStr">
@@ -10075,7 +10147,7 @@
       </c>
       <c r="C237" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D237" s="16" t="inlineStr">
@@ -10110,7 +10182,7 @@
       </c>
       <c r="C238" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D238" s="16" t="inlineStr">
@@ -10145,7 +10217,7 @@
       </c>
       <c r="C239" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D239" s="16" t="inlineStr">
@@ -10180,7 +10252,7 @@
       </c>
       <c r="C240" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D240" s="16" t="inlineStr">
@@ -10215,7 +10287,7 @@
       </c>
       <c r="C241" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D241" s="16" t="inlineStr">
@@ -10285,7 +10357,7 @@
       </c>
       <c r="C243" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D243" s="16" t="inlineStr">
@@ -10320,7 +10392,7 @@
       </c>
       <c r="C244" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D244" s="16" t="inlineStr">
@@ -10355,7 +10427,7 @@
       </c>
       <c r="C245" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D245" s="16" t="inlineStr">
@@ -10390,7 +10462,7 @@
       </c>
       <c r="C246" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D246" s="16" t="inlineStr">
@@ -10460,7 +10532,7 @@
       </c>
       <c r="C248" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D248" s="18" t="inlineStr">
@@ -10530,7 +10602,7 @@
       </c>
       <c r="C250" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D250" s="18" t="inlineStr">
@@ -10565,7 +10637,7 @@
       </c>
       <c r="C251" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D251" s="18" t="inlineStr">
@@ -10635,7 +10707,7 @@
       </c>
       <c r="C253" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D253" s="18" t="inlineStr">
@@ -10670,7 +10742,7 @@
       </c>
       <c r="C254" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D254" s="18" t="inlineStr">
@@ -10705,7 +10777,7 @@
       </c>
       <c r="C255" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D255" s="20" t="inlineStr">
@@ -10740,7 +10812,7 @@
       </c>
       <c r="C256" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D256" s="20" t="inlineStr">
@@ -10775,7 +10847,7 @@
       </c>
       <c r="C257" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D257" s="20" t="inlineStr">
@@ -10810,7 +10882,7 @@
       </c>
       <c r="C258" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D258" s="20" t="inlineStr">
@@ -10845,7 +10917,7 @@
       </c>
       <c r="C259" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D259" s="20" t="inlineStr">
@@ -10880,7 +10952,7 @@
       </c>
       <c r="C260" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D260" s="20" t="inlineStr">
@@ -10915,7 +10987,7 @@
       </c>
       <c r="C261" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D261" s="20" t="inlineStr">
@@ -10985,7 +11057,7 @@
       </c>
       <c r="C263" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D263" s="18" t="inlineStr">
@@ -11020,7 +11092,7 @@
       </c>
       <c r="C264" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D264" s="20" t="inlineStr">
@@ -11055,7 +11127,7 @@
       </c>
       <c r="C265" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D265" s="20" t="inlineStr">
@@ -11125,7 +11197,7 @@
       </c>
       <c r="C267" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D267" s="16" t="inlineStr">
@@ -11160,7 +11232,7 @@
       </c>
       <c r="C268" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D268" s="16" t="inlineStr">
@@ -11195,7 +11267,7 @@
       </c>
       <c r="C269" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D269" s="16" t="inlineStr">
@@ -11230,7 +11302,7 @@
       </c>
       <c r="C270" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D270" s="16" t="inlineStr">
@@ -11265,7 +11337,7 @@
       </c>
       <c r="C271" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D271" s="16" t="inlineStr">
@@ -11300,7 +11372,7 @@
       </c>
       <c r="C272" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D272" s="16" t="inlineStr">
@@ -11335,7 +11407,7 @@
       </c>
       <c r="C273" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D273" s="16" t="inlineStr">
@@ -11370,7 +11442,7 @@
       </c>
       <c r="C274" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D274" s="16" t="inlineStr">
@@ -11405,7 +11477,7 @@
       </c>
       <c r="C275" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D275" s="16" t="inlineStr">
@@ -11440,7 +11512,7 @@
       </c>
       <c r="C276" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D276" s="16" t="inlineStr">
@@ -11475,7 +11547,7 @@
       </c>
       <c r="C277" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D277" s="16" t="inlineStr">
@@ -11510,7 +11582,7 @@
       </c>
       <c r="C278" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D278" s="16" t="inlineStr">
@@ -11545,7 +11617,7 @@
       </c>
       <c r="C279" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D279" s="16" t="inlineStr">
@@ -11580,7 +11652,7 @@
       </c>
       <c r="C280" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D280" s="16" t="inlineStr">
@@ -11615,7 +11687,7 @@
       </c>
       <c r="C281" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D281" s="16" t="inlineStr">
@@ -11650,7 +11722,7 @@
       </c>
       <c r="C282" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D282" s="16" t="inlineStr">
@@ -11685,7 +11757,7 @@
       </c>
       <c r="C283" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D283" s="16" t="inlineStr">
@@ -11720,7 +11792,7 @@
       </c>
       <c r="C284" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D284" s="18" t="inlineStr">
@@ -11755,7 +11827,7 @@
       </c>
       <c r="C285" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D285" s="18" t="inlineStr">
@@ -11790,7 +11862,7 @@
       </c>
       <c r="C286" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D286" s="18" t="inlineStr">
@@ -11825,7 +11897,7 @@
       </c>
       <c r="C287" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D287" s="18" t="inlineStr">
@@ -11860,7 +11932,7 @@
       </c>
       <c r="C288" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D288" s="20" t="inlineStr">
@@ -11895,7 +11967,7 @@
       </c>
       <c r="C289" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D289" s="20" t="inlineStr">
@@ -11930,7 +12002,7 @@
       </c>
       <c r="C290" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D290" s="20" t="inlineStr">
@@ -12840,7 +12912,7 @@
       </c>
       <c r="C316" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D316" s="16" t="inlineStr">
@@ -12875,7 +12947,7 @@
       </c>
       <c r="C317" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D317" s="16" t="inlineStr">
@@ -12910,7 +12982,7 @@
       </c>
       <c r="C318" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D318" s="16" t="inlineStr">
@@ -12945,7 +13017,7 @@
       </c>
       <c r="C319" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D319" s="16" t="inlineStr">
@@ -12980,7 +13052,7 @@
       </c>
       <c r="C320" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D320" s="16" t="inlineStr">
@@ -13015,7 +13087,7 @@
       </c>
       <c r="C321" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D321" s="16" t="inlineStr">
@@ -13050,7 +13122,7 @@
       </c>
       <c r="C322" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D322" s="16" t="inlineStr">
@@ -13085,7 +13157,7 @@
       </c>
       <c r="C323" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D323" s="18" t="inlineStr">
@@ -13120,7 +13192,7 @@
       </c>
       <c r="C324" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D324" s="18" t="inlineStr">
@@ -13155,7 +13227,7 @@
       </c>
       <c r="C325" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D325" s="18" t="inlineStr">
@@ -14065,7 +14137,7 @@
       </c>
       <c r="C351" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D351" s="16" t="inlineStr">
@@ -14100,7 +14172,7 @@
       </c>
       <c r="C352" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D352" s="16" t="inlineStr">
@@ -14135,7 +14207,7 @@
       </c>
       <c r="C353" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D353" s="16" t="inlineStr">
@@ -14170,7 +14242,7 @@
       </c>
       <c r="C354" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D354" s="18" t="inlineStr">
@@ -14205,7 +14277,7 @@
       </c>
       <c r="C355" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D355" s="18" t="inlineStr">
@@ -14485,7 +14557,7 @@
       </c>
       <c r="C363" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D363" s="16" t="inlineStr">
@@ -14520,7 +14592,7 @@
       </c>
       <c r="C364" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D364" s="16" t="inlineStr">
@@ -14555,7 +14627,7 @@
       </c>
       <c r="C365" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D365" s="16" t="inlineStr">
@@ -14590,7 +14662,7 @@
       </c>
       <c r="C366" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D366" s="18" t="inlineStr">
@@ -14625,7 +14697,7 @@
       </c>
       <c r="C367" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D367" s="20" t="inlineStr">
@@ -14660,7 +14732,7 @@
       </c>
       <c r="C368" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D368" s="20" t="inlineStr">
@@ -14695,7 +14767,7 @@
       </c>
       <c r="C369" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D369" s="20" t="inlineStr">
@@ -14730,7 +14802,7 @@
       </c>
       <c r="C370" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D370" s="20" t="inlineStr">
@@ -14765,7 +14837,7 @@
       </c>
       <c r="C371" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D371" s="20" t="inlineStr">
@@ -14800,7 +14872,7 @@
       </c>
       <c r="C372" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D372" s="20" t="inlineStr">
@@ -14835,7 +14907,7 @@
       </c>
       <c r="C373" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D373" s="20" t="inlineStr">
@@ -14870,7 +14942,7 @@
       </c>
       <c r="C374" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D374" s="18" t="inlineStr">
@@ -14905,7 +14977,7 @@
       </c>
       <c r="C375" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D375" s="18" t="inlineStr">
@@ -14940,7 +15012,7 @@
       </c>
       <c r="C376" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D376" s="18" t="inlineStr">
@@ -15010,7 +15082,7 @@
       </c>
       <c r="C378" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D378" s="20" t="inlineStr">
@@ -15045,7 +15117,7 @@
       </c>
       <c r="C379" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D379" s="18" t="inlineStr">
@@ -15080,7 +15152,7 @@
       </c>
       <c r="C380" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D380" s="18" t="inlineStr">
@@ -15115,7 +15187,7 @@
       </c>
       <c r="C381" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D381" s="20" t="inlineStr">
@@ -15150,7 +15222,7 @@
       </c>
       <c r="C382" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D382" s="20" t="inlineStr">
@@ -15185,7 +15257,7 @@
       </c>
       <c r="C383" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D383" s="20" t="inlineStr">
@@ -15220,7 +15292,7 @@
       </c>
       <c r="C384" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D384" s="20" t="inlineStr">
@@ -15255,7 +15327,7 @@
       </c>
       <c r="C385" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D385" s="20" t="inlineStr">
@@ -15500,7 +15572,7 @@
       </c>
       <c r="C392" s="16" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D392" s="16" t="inlineStr">
@@ -15535,7 +15607,7 @@
       </c>
       <c r="C393" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D393" s="18" t="inlineStr">
@@ -15570,7 +15642,7 @@
       </c>
       <c r="C394" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D394" s="18" t="inlineStr">
@@ -15605,7 +15677,7 @@
       </c>
       <c r="C395" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D395" s="18" t="inlineStr">
@@ -15640,7 +15712,7 @@
       </c>
       <c r="C396" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D396" s="20" t="inlineStr"/>
@@ -15671,7 +15743,7 @@
       </c>
       <c r="C397" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D397" s="20" t="inlineStr"/>
@@ -15702,7 +15774,7 @@
       </c>
       <c r="C398" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D398" s="20" t="inlineStr"/>
@@ -15733,7 +15805,7 @@
       </c>
       <c r="C399" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D399" s="20" t="inlineStr"/>
@@ -15764,7 +15836,7 @@
       </c>
       <c r="C400" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D400" s="20" t="inlineStr">
@@ -15799,7 +15871,7 @@
       </c>
       <c r="C401" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D401" s="20" t="inlineStr">
@@ -15834,7 +15906,7 @@
       </c>
       <c r="C402" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D402" s="20" t="inlineStr">
@@ -15904,7 +15976,7 @@
       </c>
       <c r="C404" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D404" s="20" t="inlineStr">
@@ -15974,7 +16046,7 @@
       </c>
       <c r="C406" s="20" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D406" s="20" t="inlineStr">
@@ -16044,7 +16116,7 @@
       </c>
       <c r="C408" s="18" t="inlineStr">
         <is>
-          <t>Unknown Fire</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D408" s="18" t="inlineStr">

--- a/evac_by_zip/evac_by_zip_2026-07-29.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-07-29.xlsx
@@ -1620,7 +1620,11 @@
           <t>Level 1</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr"/>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>Malheur</t>
+        </is>
+      </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
           <t>No named fire</t>
@@ -15715,7 +15719,11 @@
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D396" s="20" t="inlineStr"/>
+      <c r="D396" s="20" t="inlineStr">
+        <is>
+          <t>Malheur</t>
+        </is>
+      </c>
       <c r="E396" s="19" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
@@ -15746,7 +15754,11 @@
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D397" s="20" t="inlineStr"/>
+      <c r="D397" s="20" t="inlineStr">
+        <is>
+          <t>Malheur</t>
+        </is>
+      </c>
       <c r="E397" s="19" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
@@ -15777,7 +15789,11 @@
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D398" s="20" t="inlineStr"/>
+      <c r="D398" s="20" t="inlineStr">
+        <is>
+          <t>Malheur</t>
+        </is>
+      </c>
       <c r="E398" s="19" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
@@ -15808,7 +15824,11 @@
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D399" s="20" t="inlineStr"/>
+      <c r="D399" s="20" t="inlineStr">
+        <is>
+          <t>Malheur</t>
+        </is>
+      </c>
       <c r="E399" s="19" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
